--- a/scouts/datasets_scouts/rodadas_local_data.xlsx
+++ b/scouts/datasets_scouts/rodadas_local_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,8 +1958,12 @@
           <t>CAM</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>INT</t>
@@ -2022,8 +2026,12 @@
           <t>BAH</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>VIT</t>
@@ -2054,8 +2062,12 @@
           <t>FLA</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>CRU</t>
@@ -2086,8 +2098,12 @@
           <t>COR</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>CFC</t>
@@ -2118,8 +2134,12 @@
           <t>REM</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>FLU</t>
@@ -2150,8 +2170,12 @@
           <t>VAS</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>PAL</t>
@@ -2182,8 +2206,12 @@
           <t>SAO</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>CHA</t>
@@ -2214,11 +2242,695 @@
           <t>GRE</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>RBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Barradão</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Nilton Santos (Engenhão)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Maracanã</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>FLU</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Vila Belmiro</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Beira-Rio</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Allianz Parque</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PAL</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>MIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Couto Pereira</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CFC</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Cícero de Souza Marques</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RBB</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mineirão</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CRU</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Arena Condá</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>GRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Allianz Parque</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PAL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Casa de Apostas Arena Fonte Nova</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>RBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Arena da Baixada</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Maião</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MIR</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Arena MRV</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Maracanã</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>FLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Vila Belmiro</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Arena do Grêmio</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>GRE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Maracanã</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Arena Condá</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>COR</t>
         </is>
       </c>
     </row>
